--- a/Dowling/dowling-vs-sep-offense.xlsx
+++ b/Dowling/dowling-vs-sep-offense.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R2ebf9756ada64bc1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Re4e7d488b4274164"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -148,6 +163,9 @@
     <t>BLUNT KEY 2</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>IOWA</t>
   </si>
   <si>
@@ -182,9 +200,6 @@
   </si>
   <si>
     <t>Return</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>PANTHERS</t>
@@ -314,7 +329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X162"/>
+  <dimension ref="A1:AC162"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -389,6 +404,21 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -398,7 +428,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -407,13 +437,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +454,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -436,13 +466,13 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +483,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -462,13 +492,13 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -488,13 +518,13 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -514,13 +544,13 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +561,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -540,13 +570,13 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -566,13 +596,13 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +613,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -592,28 +622,28 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
       <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="X9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" t="s">
         <v>36</v>
-      </c>
-      <c r="S9" t="s">
-        <v>37</v>
-      </c>
-      <c r="T9" t="s">
-        <v>38</v>
-      </c>
-      <c r="V9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -624,7 +654,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -633,19 +663,25 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>37</v>
-      </c>
-      <c r="T10" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -656,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -665,25 +701,25 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J11">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="S11" t="s">
-        <v>42</v>
-      </c>
-      <c r="T11" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="X11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -694,7 +730,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -703,16 +739,25 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-      <c r="T12" t="s">
-        <v>44</v>
+      <c r="Y12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -723,7 +768,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -732,25 +777,25 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>8</v>
       </c>
       <c r="K13" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" t="s">
-        <v>37</v>
-      </c>
-      <c r="T13" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="X13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -761,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -770,16 +815,25 @@
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" t="s">
-        <v>30</v>
-      </c>
-      <c r="T14" t="s">
-        <v>44</v>
+      <c r="Y14" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -790,7 +844,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -799,25 +853,25 @@
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15" t="s">
         <v>41</v>
       </c>
-      <c r="J15">
-        <v>3</v>
-      </c>
-      <c r="K15" t="s">
-        <v>36</v>
-      </c>
-      <c r="S15" t="s">
-        <v>45</v>
-      </c>
-      <c r="T15" t="s">
-        <v>46</v>
+      <c r="X15" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -828,7 +882,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -837,27 +891,30 @@
         <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J16">
         <v>12</v>
       </c>
       <c r="K16" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" t="s">
-        <v>47</v>
-      </c>
-      <c r="T16" t="s">
-        <v>48</v>
-      </c>
-      <c r="W16">
+        <v>41</v>
+      </c>
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="X16" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -869,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -878,21 +935,30 @@
         <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" t="s">
-        <v>30</v>
-      </c>
-      <c r="S17" t="s">
-        <v>49</v>
-      </c>
-      <c r="T17" t="s">
-        <v>50</v>
-      </c>
-      <c r="W17">
+      <c r="X17" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -904,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -913,24 +979,24 @@
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" t="s">
-        <v>51</v>
-      </c>
-      <c r="W18">
+        <v>41</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -942,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -951,15 +1017,15 @@
         <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
-      </c>
-      <c r="W19">
+        <v>59</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -971,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -980,13 +1046,13 @@
         <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
@@ -997,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1006,13 +1072,13 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -1023,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1032,13 +1098,13 @@
         <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -1049,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1058,13 +1124,13 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
@@ -1075,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1084,13 +1150,13 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -1101,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -1110,13 +1176,13 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
@@ -1127,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1136,28 +1202,28 @@
         <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>57</v>
-      </c>
-      <c r="S26" t="s">
-        <v>37</v>
-      </c>
-      <c r="T26" t="s">
-        <v>58</v>
-      </c>
-      <c r="V26" t="s">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="X26" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -1168,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1177,25 +1243,25 @@
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J27">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>36</v>
-      </c>
-      <c r="S27" t="s">
-        <v>59</v>
-      </c>
-      <c r="T27" t="s">
-        <v>60</v>
+        <v>41</v>
+      </c>
+      <c r="X27" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -1206,7 +1272,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1215,28 +1281,28 @@
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H28" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I28" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>57</v>
-      </c>
-      <c r="S28" t="s">
-        <v>61</v>
-      </c>
-      <c r="T28" t="s">
-        <v>62</v>
-      </c>
-      <c r="V28" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="X28" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1247,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1256,13 +1322,13 @@
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I29" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -1273,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1282,13 +1348,13 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
@@ -1299,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1308,13 +1374,13 @@
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I31" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
@@ -1325,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1334,13 +1400,13 @@
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H32" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I32" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -1351,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1360,13 +1426,13 @@
         <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -1377,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1386,13 +1452,13 @@
         <v>4</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H34" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -1403,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -1412,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H35" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -1429,7 +1495,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1438,13 +1504,13 @@
         <v>10</v>
       </c>
       <c r="G36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I36" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
@@ -1455,7 +1521,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1464,13 +1530,13 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1481,7 +1547,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -1490,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H38" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I38" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39">
@@ -1507,7 +1573,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1516,13 +1582,13 @@
         <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
@@ -1533,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1542,13 +1608,13 @@
         <v>5</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
@@ -1559,7 +1625,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1568,13 +1634,13 @@
         <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
@@ -1585,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -1594,13 +1660,13 @@
         <v>6</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I42" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -1611,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -1620,13 +1686,13 @@
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -1637,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -1646,13 +1712,13 @@
         <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H44" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
@@ -1663,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1672,13 +1738,13 @@
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I45" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -1689,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -1698,13 +1764,13 @@
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I46" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47">
@@ -1715,7 +1781,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -1724,13 +1790,13 @@
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48">
@@ -1741,7 +1807,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1750,13 +1816,13 @@
         <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I48" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
@@ -1767,7 +1833,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1776,25 +1842,28 @@
         <v>10</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H49" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49" t="s">
+        <v>50</v>
+      </c>
+      <c r="P49" t="s">
         <v>29</v>
       </c>
-      <c r="I49" t="s">
-        <v>30</v>
-      </c>
-      <c r="J49">
-        <v>2</v>
-      </c>
-      <c r="K49" t="s">
-        <v>57</v>
-      </c>
-      <c r="S49" t="s">
-        <v>47</v>
-      </c>
-      <c r="T49" t="s">
-        <v>67</v>
+      <c r="X49" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="50">
@@ -1805,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1814,25 +1883,25 @@
         <v>8</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H50" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I50" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J50">
         <v>7</v>
       </c>
       <c r="K50" t="s">
-        <v>36</v>
-      </c>
-      <c r="S50" t="s">
-        <v>68</v>
-      </c>
-      <c r="T50" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="X50" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="51">
@@ -1843,7 +1912,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -1852,25 +1921,25 @@
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H51" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I51" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>57</v>
-      </c>
-      <c r="S51" t="s">
-        <v>70</v>
-      </c>
-      <c r="T51" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="X51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -1881,7 +1950,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -1890,13 +1959,13 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H52" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I52" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53">
@@ -1907,7 +1976,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1916,15 +1985,15 @@
         <v>10</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H53" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q53">
+        <v>35</v>
+      </c>
+      <c r="V53">
         <v>0</v>
       </c>
     </row>
@@ -1936,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1945,13 +2014,13 @@
         <v>10</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
@@ -1962,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -1971,13 +2040,13 @@
         <v>6</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
@@ -1988,7 +2057,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -1997,7 +2066,7 @@
         <v>4</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -2008,7 +2077,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -2017,13 +2086,13 @@
         <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H57" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I57" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -2034,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2043,13 +2112,13 @@
         <v>10</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59">
@@ -2060,7 +2129,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2069,13 +2138,13 @@
         <v>10</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I59" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60">
@@ -2086,7 +2155,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2095,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="G60" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
@@ -2112,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -2121,13 +2190,13 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I61" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62">
@@ -2138,7 +2207,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2147,13 +2216,13 @@
         <v>10</v>
       </c>
       <c r="G62" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I62" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -2164,7 +2233,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2173,13 +2242,13 @@
         <v>10</v>
       </c>
       <c r="G63" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H63" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I63" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
@@ -2190,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2199,25 +2268,25 @@
         <v>10</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>36</v>
-      </c>
-      <c r="S64" t="s">
-        <v>37</v>
-      </c>
-      <c r="T64" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X64" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="65">
@@ -2228,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -2237,25 +2306,25 @@
         <v>5</v>
       </c>
       <c r="G65" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J65">
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>36</v>
-      </c>
-      <c r="S65" t="s">
-        <v>37</v>
-      </c>
-      <c r="T65" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X65" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="66">
@@ -2266,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -2275,25 +2344,25 @@
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J66">
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>36</v>
-      </c>
-      <c r="S66" t="s">
-        <v>37</v>
-      </c>
-      <c r="T66" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X66" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="67">
@@ -2304,7 +2373,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2313,25 +2382,25 @@
         <v>10</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I67" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J67">
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>36</v>
-      </c>
-      <c r="S67" t="s">
-        <v>37</v>
-      </c>
-      <c r="T67" t="s">
-        <v>75</v>
+        <v>41</v>
+      </c>
+      <c r="X67" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -2342,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2351,25 +2420,25 @@
         <v>10</v>
       </c>
       <c r="G68" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I68" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J68">
         <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>36</v>
-      </c>
-      <c r="S68" t="s">
-        <v>37</v>
-      </c>
-      <c r="T68" t="s">
-        <v>76</v>
+        <v>41</v>
+      </c>
+      <c r="X68" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="69">
@@ -2380,7 +2449,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -2389,13 +2458,13 @@
         <v>10</v>
       </c>
       <c r="G69" t="s">
-        <v>35</v>
-      </c>
-      <c r="S69" t="s">
-        <v>37</v>
-      </c>
-      <c r="T69" t="s">
-        <v>77</v>
+        <v>40</v>
+      </c>
+      <c r="X69" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -2406,7 +2475,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2415,28 +2484,28 @@
         <v>13</v>
       </c>
       <c r="G70" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H70" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I70" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J70">
         <v>41</v>
       </c>
       <c r="K70" t="s">
+        <v>41</v>
+      </c>
+      <c r="X70" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA70" t="s">
         <v>36</v>
-      </c>
-      <c r="S70" t="s">
-        <v>49</v>
-      </c>
-      <c r="T70" t="s">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -2447,7 +2516,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -2459,13 +2528,13 @@
         <v>3</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H71" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I71" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72">
@@ -2476,7 +2545,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -2485,13 +2554,13 @@
         <v>10</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H72" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I72" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -2502,7 +2571,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -2511,13 +2580,13 @@
         <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I73" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -2528,7 +2597,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -2537,13 +2606,13 @@
         <v>2</v>
       </c>
       <c r="G74" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I74" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
@@ -2554,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -2563,13 +2632,13 @@
         <v>10</v>
       </c>
       <c r="G75" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H75" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
@@ -2580,7 +2649,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2589,13 +2658,13 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I76" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
@@ -2606,7 +2675,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2615,25 +2684,25 @@
         <v>10</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H77" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I77" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J77">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>57</v>
-      </c>
-      <c r="S77" t="s">
-        <v>37</v>
-      </c>
-      <c r="T77" t="s">
-        <v>39</v>
+        <v>50</v>
+      </c>
+      <c r="X77" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="78">
@@ -2644,7 +2713,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -2653,25 +2722,25 @@
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H78" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J78">
         <v>5</v>
       </c>
       <c r="K78" t="s">
-        <v>36</v>
-      </c>
-      <c r="S78" t="s">
-        <v>45</v>
-      </c>
-      <c r="T78" t="s">
-        <v>80</v>
+        <v>41</v>
+      </c>
+      <c r="X78" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="79">
@@ -2682,7 +2751,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -2691,13 +2760,13 @@
         <v>4</v>
       </c>
       <c r="G79" t="s">
-        <v>35</v>
-      </c>
-      <c r="S79" t="s">
-        <v>37</v>
-      </c>
-      <c r="T79" t="s">
-        <v>77</v>
+        <v>40</v>
+      </c>
+      <c r="X79" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="80">
@@ -2708,7 +2777,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -2717,13 +2786,13 @@
         <v>8</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I80" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81">
@@ -2734,7 +2803,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -2743,13 +2812,13 @@
         <v>10</v>
       </c>
       <c r="G81" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H81" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I81" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82">
@@ -2760,7 +2829,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -2769,13 +2838,13 @@
         <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H82" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I82" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
@@ -2786,7 +2855,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -2795,13 +2864,13 @@
         <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I83" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -2812,7 +2881,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2821,13 +2890,13 @@
         <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H84" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I84" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85">
@@ -2838,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2847,13 +2916,13 @@
         <v>10</v>
       </c>
       <c r="G85" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I85" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86">
@@ -2864,7 +2933,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -2876,13 +2945,13 @@
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H86" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -2893,7 +2962,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2902,13 +2971,13 @@
         <v>10</v>
       </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H87" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I87" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -2919,7 +2988,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -2928,25 +2997,25 @@
         <v>10</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I88" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>57</v>
-      </c>
-      <c r="S88" t="s">
-        <v>37</v>
-      </c>
-      <c r="T88" t="s">
-        <v>81</v>
+        <v>50</v>
+      </c>
+      <c r="X88" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="89">
@@ -2957,7 +3026,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -2966,25 +3035,25 @@
         <v>10</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I89" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J89">
         <v>9</v>
       </c>
       <c r="K89" t="s">
-        <v>36</v>
-      </c>
-      <c r="S89" t="s">
-        <v>61</v>
-      </c>
-      <c r="T89" t="s">
-        <v>82</v>
+        <v>41</v>
+      </c>
+      <c r="X89" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="90">
@@ -2995,7 +3064,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -3004,25 +3073,25 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H90" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I90" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J90">
         <v>3</v>
       </c>
       <c r="K90" t="s">
-        <v>36</v>
-      </c>
-      <c r="S90" t="s">
-        <v>45</v>
-      </c>
-      <c r="T90" t="s">
-        <v>83</v>
+        <v>41</v>
+      </c>
+      <c r="X90" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -3033,7 +3102,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3042,25 +3111,25 @@
         <v>10</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I91" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J91">
         <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>36</v>
-      </c>
-      <c r="S91" t="s">
-        <v>37</v>
-      </c>
-      <c r="T91" t="s">
-        <v>76</v>
+        <v>41</v>
+      </c>
+      <c r="X91" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="92">
@@ -3071,7 +3140,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -3080,25 +3149,25 @@
         <v>5</v>
       </c>
       <c r="G92" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H92" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I92" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J92">
         <v>8</v>
       </c>
       <c r="K92" t="s">
-        <v>36</v>
-      </c>
-      <c r="S92" t="s">
-        <v>42</v>
-      </c>
-      <c r="T92" t="s">
-        <v>84</v>
+        <v>41</v>
+      </c>
+      <c r="X92" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="93">
@@ -3109,7 +3178,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3118,25 +3187,25 @@
         <v>10</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H93" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I93" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J93">
         <v>18</v>
       </c>
       <c r="K93" t="s">
-        <v>36</v>
-      </c>
-      <c r="S93" t="s">
-        <v>59</v>
-      </c>
-      <c r="T93" t="s">
-        <v>85</v>
+        <v>41</v>
+      </c>
+      <c r="X93" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -3147,7 +3216,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3156,25 +3225,25 @@
         <v>10</v>
       </c>
       <c r="G94" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H94" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I94" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>57</v>
-      </c>
-      <c r="S94" t="s">
-        <v>37</v>
-      </c>
-      <c r="T94" t="s">
-        <v>86</v>
+        <v>50</v>
+      </c>
+      <c r="X94" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="95">
@@ -3185,7 +3254,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -3194,25 +3263,25 @@
         <v>10</v>
       </c>
       <c r="G95" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H95" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I95" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J95">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>57</v>
-      </c>
-      <c r="S95" t="s">
-        <v>37</v>
-      </c>
-      <c r="T95" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="X95" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="96">
@@ -3223,7 +3292,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -3232,25 +3301,25 @@
         <v>10</v>
       </c>
       <c r="G96" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H96" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I96" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>57</v>
-      </c>
-      <c r="S96" t="s">
-        <v>59</v>
-      </c>
-      <c r="T96" t="s">
-        <v>87</v>
+        <v>50</v>
+      </c>
+      <c r="X96" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="97">
@@ -3261,7 +3330,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -3270,13 +3339,13 @@
         <v>10</v>
       </c>
       <c r="G97" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H97" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I97" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98">
@@ -3287,7 +3356,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D98">
         <v>4</v>
@@ -3296,13 +3365,13 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H98" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I98" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99">
@@ -3313,7 +3382,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3322,13 +3391,13 @@
         <v>10</v>
       </c>
       <c r="G99" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H99" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I99" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100">
@@ -3339,7 +3408,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -3348,13 +3417,13 @@
         <v>9</v>
       </c>
       <c r="G100" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I100" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
@@ -3365,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3374,13 +3443,13 @@
         <v>10</v>
       </c>
       <c r="G101" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H101" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I101" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102">
@@ -3391,7 +3460,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3400,13 +3469,13 @@
         <v>10</v>
       </c>
       <c r="G102" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H102" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I102" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103">
@@ -3417,7 +3486,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -3426,13 +3495,13 @@
         <v>10</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I103" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="104">
@@ -3443,7 +3512,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3452,13 +3521,13 @@
         <v>10</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I104" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105">
@@ -3469,7 +3538,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -3478,13 +3547,13 @@
         <v>10</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I105" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="106">
@@ -3495,7 +3564,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -3504,13 +3573,13 @@
         <v>8</v>
       </c>
       <c r="G106" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H106" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I106" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107">
@@ -3521,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -3530,13 +3599,13 @@
         <v>8</v>
       </c>
       <c r="G107" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H107" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I107" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="108">
@@ -3547,7 +3616,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -3556,13 +3625,13 @@
         <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H108" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109">
@@ -3573,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -3582,13 +3651,13 @@
         <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H109" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I109" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110">
@@ -3599,7 +3668,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -3608,13 +3677,13 @@
         <v>1</v>
       </c>
       <c r="G110" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H110" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I110" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111">
@@ -3625,7 +3694,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3634,13 +3703,13 @@
         <v>10</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H111" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I111" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="112">
@@ -3651,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -3660,13 +3729,13 @@
         <v>9</v>
       </c>
       <c r="G112" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H112" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I112" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113">
@@ -3677,7 +3746,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -3686,13 +3755,13 @@
         <v>8</v>
       </c>
       <c r="G113" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H113" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I113" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114">
@@ -3703,7 +3772,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D114">
         <v>4</v>
@@ -3712,13 +3781,13 @@
         <v>4</v>
       </c>
       <c r="G114" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H114" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I114" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="115">
@@ -3729,7 +3798,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3738,13 +3807,13 @@
         <v>10</v>
       </c>
       <c r="G115" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H115" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I115" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="116">
@@ -3755,7 +3824,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -3764,25 +3833,25 @@
         <v>10</v>
       </c>
       <c r="G116" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H116" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I116" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J116">
         <v>8</v>
       </c>
       <c r="K116" t="s">
-        <v>36</v>
-      </c>
-      <c r="S116" t="s">
-        <v>37</v>
-      </c>
-      <c r="T116" t="s">
-        <v>90</v>
+        <v>41</v>
+      </c>
+      <c r="X116" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="117">
@@ -3793,7 +3862,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D117">
         <v>2</v>
@@ -3802,25 +3871,25 @@
         <v>2</v>
       </c>
       <c r="G117" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H117" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I117" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>57</v>
-      </c>
-      <c r="S117" t="s">
-        <v>37</v>
-      </c>
-      <c r="T117" t="s">
-        <v>90</v>
+        <v>50</v>
+      </c>
+      <c r="X117" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="118">
@@ -3831,7 +3900,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D118">
         <v>3</v>
@@ -3840,25 +3909,25 @@
         <v>2</v>
       </c>
       <c r="G118" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H118" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I118" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J118">
         <v>17</v>
       </c>
       <c r="K118" t="s">
-        <v>36</v>
-      </c>
-      <c r="S118" t="s">
-        <v>42</v>
-      </c>
-      <c r="T118" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="X118" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="119">
@@ -3869,7 +3938,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3878,28 +3947,28 @@
         <v>10</v>
       </c>
       <c r="G119" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H119" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I119" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>57</v>
-      </c>
-      <c r="S119" t="s">
-        <v>49</v>
-      </c>
-      <c r="T119" t="s">
-        <v>79</v>
-      </c>
-      <c r="V119" t="s">
-        <v>35</v>
+        <v>50</v>
+      </c>
+      <c r="X119" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA119" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="120">
@@ -3910,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -3919,25 +3988,25 @@
         <v>10</v>
       </c>
       <c r="G120" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H120" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J120">
         <v>16</v>
       </c>
       <c r="K120" t="s">
-        <v>36</v>
-      </c>
-      <c r="S120" t="s">
-        <v>37</v>
-      </c>
-      <c r="T120" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X120" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="121">
@@ -3948,7 +4017,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -3957,25 +4026,25 @@
         <v>10</v>
       </c>
       <c r="G121" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H121" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J121">
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>57</v>
-      </c>
-      <c r="S121" t="s">
-        <v>45</v>
-      </c>
-      <c r="T121" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="X121" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="122">
@@ -3986,7 +4055,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -3995,27 +4064,27 @@
         <v>7</v>
       </c>
       <c r="G122" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H122" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I122" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>57</v>
-      </c>
-      <c r="S122" t="s">
-        <v>37</v>
-      </c>
-      <c r="T122" t="s">
-        <v>39</v>
-      </c>
-      <c r="W122">
+        <v>50</v>
+      </c>
+      <c r="X122" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB122">
         <v>8</v>
       </c>
     </row>
@@ -4027,7 +4096,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4036,27 +4105,27 @@
         <v>5</v>
       </c>
       <c r="G123" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I123" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J123">
         <v>15</v>
       </c>
       <c r="K123" t="s">
-        <v>36</v>
-      </c>
-      <c r="S123" t="s">
-        <v>61</v>
-      </c>
-      <c r="T123" t="s">
-        <v>92</v>
-      </c>
-      <c r="W123">
+        <v>41</v>
+      </c>
+      <c r="X123" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB123">
         <v>8</v>
       </c>
     </row>
@@ -4068,7 +4137,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4077,27 +4146,27 @@
         <v>10</v>
       </c>
       <c r="G124" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I124" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J124">
         <v>8</v>
       </c>
       <c r="K124" t="s">
-        <v>36</v>
-      </c>
-      <c r="S124" t="s">
-        <v>45</v>
-      </c>
-      <c r="T124" t="s">
-        <v>38</v>
-      </c>
-      <c r="W124">
+        <v>41</v>
+      </c>
+      <c r="X124" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB124">
         <v>8</v>
       </c>
     </row>
@@ -4109,7 +4178,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -4118,25 +4187,25 @@
         <v>2</v>
       </c>
       <c r="G125" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H125" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I125" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J125">
         <v>12</v>
       </c>
       <c r="K125" t="s">
-        <v>36</v>
-      </c>
-      <c r="S125" t="s">
-        <v>93</v>
-      </c>
-      <c r="T125" t="s">
-        <v>94</v>
+        <v>41</v>
+      </c>
+      <c r="X125" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="126">
@@ -4147,7 +4216,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4159,13 +4228,13 @@
         <v>3</v>
       </c>
       <c r="G126" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H126" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I126" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127">
@@ -4176,7 +4245,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4185,13 +4254,13 @@
         <v>10</v>
       </c>
       <c r="G127" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I127" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
@@ -4202,7 +4271,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4211,13 +4280,13 @@
         <v>10</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H128" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I128" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="129">
@@ -4228,7 +4297,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -4237,15 +4306,15 @@
         <v>7</v>
       </c>
       <c r="G129" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H129" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I129" t="s">
-        <v>95</v>
-      </c>
-      <c r="W129">
+        <v>100</v>
+      </c>
+      <c r="AB129">
         <v>7</v>
       </c>
     </row>
@@ -4257,7 +4326,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4266,27 +4335,27 @@
         <v>10</v>
       </c>
       <c r="G130" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H130" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I130" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J130">
         <v>17</v>
       </c>
       <c r="K130" t="s">
-        <v>36</v>
-      </c>
-      <c r="S130" t="s">
-        <v>37</v>
-      </c>
-      <c r="T130" t="s">
-        <v>38</v>
-      </c>
-      <c r="W130">
+        <v>41</v>
+      </c>
+      <c r="X130" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB130">
         <v>9</v>
       </c>
     </row>
@@ -4298,7 +4367,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4307,27 +4376,27 @@
         <v>10</v>
       </c>
       <c r="G131" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H131" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I131" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J131">
         <v>10</v>
       </c>
       <c r="K131" t="s">
-        <v>36</v>
-      </c>
-      <c r="S131" t="s">
-        <v>37</v>
-      </c>
-      <c r="T131" t="s">
-        <v>39</v>
-      </c>
-      <c r="W131">
+        <v>41</v>
+      </c>
+      <c r="X131" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB131">
         <v>9</v>
       </c>
     </row>
@@ -4339,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4348,25 +4417,25 @@
         <v>10</v>
       </c>
       <c r="G132" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H132" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I132" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J132">
         <v>4</v>
       </c>
       <c r="K132" t="s">
-        <v>36</v>
-      </c>
-      <c r="S132" t="s">
-        <v>37</v>
-      </c>
-      <c r="T132" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="X132" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="133">
@@ -4377,7 +4446,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4389,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="G133" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H133" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I133" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134">
@@ -4406,7 +4475,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4415,13 +4484,13 @@
         <v>10</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H134" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I134" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135">
@@ -4432,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4441,13 +4510,13 @@
         <v>10</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I135" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136">
@@ -4458,7 +4527,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -4467,13 +4536,13 @@
         <v>1</v>
       </c>
       <c r="G136" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H136" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I136" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137">
@@ -4484,7 +4553,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4493,13 +4562,13 @@
         <v>10</v>
       </c>
       <c r="G137" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H137" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I137" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="138">
@@ -4510,7 +4579,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -4519,13 +4588,13 @@
         <v>10</v>
       </c>
       <c r="G138" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H138" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I138" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="139">
@@ -4536,7 +4605,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4545,13 +4614,13 @@
         <v>10</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I139" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140">
@@ -4562,7 +4631,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -4571,13 +4640,13 @@
         <v>10</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H140" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I140" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141">
@@ -4588,7 +4657,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -4597,28 +4666,28 @@
         <v>10</v>
       </c>
       <c r="G141" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H141" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I141" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q141">
+        <v>50</v>
+      </c>
+      <c r="V141">
         <v>0</v>
       </c>
-      <c r="S141" t="s">
-        <v>45</v>
-      </c>
-      <c r="T141" t="s">
-        <v>96</v>
+      <c r="X141" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="142">
@@ -4629,7 +4698,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -4638,22 +4707,25 @@
         <v>10</v>
       </c>
       <c r="G142" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H142" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I142" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
-      <c r="S142" t="s">
-        <v>37</v>
-      </c>
-      <c r="T142" t="s">
-        <v>39</v>
+      <c r="K142" t="s">
+        <v>50</v>
+      </c>
+      <c r="X142" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="143">
@@ -4664,7 +4736,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -4673,25 +4745,25 @@
         <v>10</v>
       </c>
       <c r="G143" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H143" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I143" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>57</v>
-      </c>
-      <c r="S143" t="s">
-        <v>42</v>
-      </c>
-      <c r="T143" t="s">
-        <v>97</v>
+        <v>50</v>
+      </c>
+      <c r="X143" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="144">
@@ -4702,7 +4774,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>4</v>
@@ -4711,13 +4783,13 @@
         <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H144" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I144" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145">
@@ -4728,7 +4800,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4737,13 +4809,13 @@
         <v>10</v>
       </c>
       <c r="G145" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H145" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I145" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146">
@@ -4754,7 +4826,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -4763,13 +4835,13 @@
         <v>10</v>
       </c>
       <c r="G146" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H146" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I146" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147">
@@ -4780,7 +4852,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4789,13 +4861,13 @@
         <v>10</v>
       </c>
       <c r="G147" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H147" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I147" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148">
@@ -4806,7 +4878,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D148">
         <v>2</v>
@@ -4815,13 +4887,13 @@
         <v>13</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H148" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I148" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149">
@@ -4832,7 +4904,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -4841,13 +4913,13 @@
         <v>13</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H149" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I149" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="150">
@@ -4858,7 +4930,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4867,13 +4939,13 @@
         <v>10</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H150" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I150" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="151">
@@ -4884,7 +4956,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -4893,13 +4965,13 @@
         <v>4</v>
       </c>
       <c r="G151" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H151" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I151" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152">
@@ -4910,7 +4982,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4919,13 +4991,13 @@
         <v>10</v>
       </c>
       <c r="G152" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H152" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I152" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="153">
@@ -4936,7 +5008,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -4945,13 +5017,13 @@
         <v>6</v>
       </c>
       <c r="G153" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H153" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I153" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154">
@@ -4962,7 +5034,7 @@
         <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -4971,13 +5043,13 @@
         <v>6</v>
       </c>
       <c r="G154" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H154" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I154" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="155">
@@ -4988,7 +5060,7 @@
         <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -4997,13 +5069,13 @@
         <v>10</v>
       </c>
       <c r="G155" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H155" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I155" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156">
@@ -5014,7 +5086,7 @@
         <v>4</v>
       </c>
       <c r="C156" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D156">
         <v>2</v>
@@ -5023,13 +5095,13 @@
         <v>16</v>
       </c>
       <c r="G156" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H156" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I156" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="157">
@@ -5040,7 +5112,7 @@
         <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D157">
         <v>3</v>
@@ -5049,13 +5121,13 @@
         <v>16</v>
       </c>
       <c r="G157" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H157" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I157" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="158">
@@ -5066,7 +5138,7 @@
         <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -5075,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="G158" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="159">
@@ -5086,7 +5158,7 @@
         <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D159">
         <v>4</v>
@@ -5095,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="G159" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="160">
@@ -5106,7 +5178,7 @@
         <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D160">
         <v>4</v>
@@ -5115,13 +5187,13 @@
         <v>1</v>
       </c>
       <c r="G160" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H160" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="I160" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="161">
@@ -5132,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -5141,13 +5213,13 @@
         <v>10</v>
       </c>
       <c r="G161" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H161" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I161" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="162">
@@ -5158,7 +5230,7 @@
         <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -5167,22 +5239,22 @@
         <v>10</v>
       </c>
       <c r="G162" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H162" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I162" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>57</v>
-      </c>
-      <c r="T162" t="s">
-        <v>98</v>
+        <v>50</v>
+      </c>
+      <c r="Y162" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
